--- a/programacao-hoje.xlsx
+++ b/programacao-hoje.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Meu Drive\Prime\Produção\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5700E7BC-D03B-4156-9925-97DB78FAB24C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DCE5BE7A-0879-425D-8FAB-EDF0219C8141}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="1" activeTab="6" xr2:uid="{B44A584A-541A-489B-A537-1CEFC190DF9A}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="1" activeTab="7" xr2:uid="{B44A584A-541A-489B-A537-1CEFC190DF9A}"/>
   </bookViews>
   <sheets>
     <sheet name="FAVINCO 18 ao 25" sheetId="5" r:id="rId1"/>
@@ -50,7 +50,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1762" uniqueCount="252">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1777" uniqueCount="262">
   <si>
     <t>Programação Onduladeira — ABAPEL</t>
   </si>
@@ -595,13 +595,7 @@
     <t>03/07/2026</t>
   </si>
   <si>
-    <t>CURITIBOX</t>
-  </si>
-  <si>
     <t>1590x1590</t>
-  </si>
-  <si>
-    <t>Programação Onduladeira — CURITIBOX</t>
   </si>
   <si>
     <t>1140x1700</t>
@@ -807,6 +801,42 @@
   <si>
     <t>Programação Onduladeira — ABAPEL3</t>
   </si>
+  <si>
+    <t>0.870</t>
+  </si>
+  <si>
+    <t>205X460X205</t>
+  </si>
+  <si>
+    <t>1158.0</t>
+  </si>
+  <si>
+    <t>0.3217</t>
+  </si>
+  <si>
+    <t>19.30</t>
+  </si>
+  <si>
+    <t>430.7</t>
+  </si>
+  <si>
+    <t>0.0333</t>
+  </si>
+  <si>
+    <t>890x1950</t>
+  </si>
+  <si>
+    <t>Programação Onduladeira — J FER - A4 Emb.</t>
+  </si>
+  <si>
+    <t>JFER</t>
+  </si>
+  <si>
+    <t>A4 Emb</t>
+  </si>
+  <si>
+    <t>PRIME 032</t>
+  </si>
 </sst>
 </file>
 
@@ -987,7 +1017,7 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="57">
+  <cellXfs count="60">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1143,6 +1173,15 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="14" fontId="10" fillId="6" borderId="1" xfId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1255,15 +1294,15 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>10</xdr:col>
-      <xdr:colOff>91440</xdr:colOff>
+      <xdr:colOff>121920</xdr:colOff>
       <xdr:row>16</xdr:row>
-      <xdr:rowOff>30480</xdr:rowOff>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>25</xdr:col>
-      <xdr:colOff>301615</xdr:colOff>
+      <xdr:colOff>332095</xdr:colOff>
       <xdr:row>26</xdr:row>
-      <xdr:rowOff>91703</xdr:rowOff>
+      <xdr:rowOff>61223</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1286,8 +1325,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="5139690" y="3268980"/>
-          <a:ext cx="4591675" cy="1775723"/>
+          <a:off x="5166360" y="3284220"/>
+          <a:ext cx="4599295" cy="1813823"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -66562,7 +66601,7 @@
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="4.88671875" style="20" customWidth="1"/>
-    <col min="2" max="2" width="10.77734375" style="20" hidden="1" customWidth="1"/>
+    <col min="2" max="2" width="10.77734375" style="20" customWidth="1"/>
     <col min="3" max="3" width="7.77734375" style="20" customWidth="1"/>
     <col min="4" max="4" width="11.77734375" style="20" hidden="1" customWidth="1"/>
     <col min="5" max="5" width="10.77734375" style="20" customWidth="1"/>
@@ -66593,7 +66632,7 @@
   <sheetData>
     <row r="1" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="56" t="s">
-        <v>183</v>
+        <v>258</v>
       </c>
       <c r="B1" s="56" t="s">
         <v>32</v>
@@ -66767,8 +66806,8 @@
       <c r="A3" s="38">
         <v>1</v>
       </c>
-      <c r="B3" s="43" t="s">
-        <v>181</v>
+      <c r="B3" s="58" t="s">
+        <v>260</v>
       </c>
       <c r="C3" s="38" t="s">
         <v>66</v>
@@ -66846,15 +66885,15 @@
         <v>100</v>
       </c>
       <c r="AB3" s="38" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="4" spans="1:28" x14ac:dyDescent="0.3">
       <c r="A4" s="38">
         <v>2</v>
       </c>
-      <c r="B4" s="43" t="s">
-        <v>181</v>
+      <c r="B4" s="58" t="s">
+        <v>259</v>
       </c>
       <c r="C4" s="38" t="s">
         <v>66</v>
@@ -67068,7 +67107,7 @@
   <sheetData>
     <row r="1" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="55" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="B1" s="55" t="s">
         <v>32</v>
@@ -67243,10 +67282,10 @@
         <v>1</v>
       </c>
       <c r="B3" s="23" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="C3" s="49" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="D3" s="49" t="s">
         <v>180</v>
@@ -67258,7 +67297,7 @@
         <v>261570</v>
       </c>
       <c r="G3" s="49" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="H3" s="49">
         <v>2000</v>
@@ -67303,7 +67342,7 @@
         <v>1.29E-2</v>
       </c>
       <c r="V3" s="44" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="W3" s="44" t="s">
         <v>36</v>
@@ -67321,7 +67360,7 @@
         <v>44</v>
       </c>
       <c r="AB3" s="44" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
     </row>
     <row r="4" spans="1:28" x14ac:dyDescent="0.3">
@@ -67329,7 +67368,7 @@
         <v>2</v>
       </c>
       <c r="B4" s="23" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="C4" s="49" t="s">
         <v>66</v>
@@ -67344,7 +67383,7 @@
         <v>261564</v>
       </c>
       <c r="G4" s="49" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="H4" s="49">
         <v>1500</v>
@@ -67407,7 +67446,7 @@
         <v>44</v>
       </c>
       <c r="AB4" s="44" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
     </row>
     <row r="5" spans="1:28" x14ac:dyDescent="0.3">
@@ -67415,7 +67454,7 @@
         <v>3</v>
       </c>
       <c r="B5" s="23" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="C5" s="49" t="s">
         <v>66</v>
@@ -67430,7 +67469,7 @@
         <v>261565</v>
       </c>
       <c r="G5" s="49" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="H5" s="49">
         <v>2000</v>
@@ -67493,7 +67532,7 @@
         <v>44</v>
       </c>
       <c r="AB5" s="44" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
     </row>
     <row r="6" spans="1:28" x14ac:dyDescent="0.3">
@@ -67501,7 +67540,7 @@
         <v>4</v>
       </c>
       <c r="B6" s="23" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="C6" s="49" t="s">
         <v>66</v>
@@ -67516,7 +67555,7 @@
         <v>261566</v>
       </c>
       <c r="G6" s="49" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="H6" s="49">
         <v>4000</v>
@@ -67579,7 +67618,7 @@
         <v>37</v>
       </c>
       <c r="AB6" s="44" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
     </row>
     <row r="7" spans="1:28" x14ac:dyDescent="0.3">
@@ -67587,10 +67626,10 @@
         <v>5</v>
       </c>
       <c r="B7" s="23" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="C7" s="49" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="D7" s="49" t="s">
         <v>180</v>
@@ -67602,7 +67641,7 @@
         <v>261569</v>
       </c>
       <c r="G7" s="49" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="H7" s="49">
         <v>3000</v>
@@ -67647,7 +67686,7 @@
         <v>1.43E-2</v>
       </c>
       <c r="V7" s="44" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="W7" s="44" t="s">
         <v>36</v>
@@ -67665,7 +67704,7 @@
         <v>44</v>
       </c>
       <c r="AB7" s="44" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
     </row>
     <row r="8" spans="1:28" x14ac:dyDescent="0.3">
@@ -67673,10 +67712,10 @@
         <v>6</v>
       </c>
       <c r="B8" s="23" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="C8" s="49" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="D8" s="49" t="s">
         <v>180</v>
@@ -67688,7 +67727,7 @@
         <v>261572</v>
       </c>
       <c r="G8" s="49" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="H8" s="49">
         <v>1000</v>
@@ -67733,7 +67772,7 @@
         <v>1.6E-2</v>
       </c>
       <c r="V8" s="44" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="W8" s="44" t="s">
         <v>36</v>
@@ -67751,7 +67790,7 @@
         <v>100</v>
       </c>
       <c r="AB8" s="44" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
     </row>
     <row r="9" spans="1:28" x14ac:dyDescent="0.3">
@@ -67759,7 +67798,7 @@
         <v>7</v>
       </c>
       <c r="B9" s="23" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="C9" s="49" t="s">
         <v>66</v>
@@ -67774,7 +67813,7 @@
         <v>261567</v>
       </c>
       <c r="G9" s="49" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="H9" s="49">
         <v>2000</v>
@@ -67837,7 +67876,7 @@
         <v>100</v>
       </c>
       <c r="AB9" s="44" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
     </row>
     <row r="10" spans="1:28" x14ac:dyDescent="0.3">
@@ -67845,7 +67884,7 @@
         <v>8</v>
       </c>
       <c r="B10" s="23" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="C10" s="49" t="s">
         <v>66</v>
@@ -67860,7 +67899,7 @@
         <v>261568</v>
       </c>
       <c r="G10" s="49" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="H10" s="49">
         <v>1000</v>
@@ -67923,7 +67962,7 @@
         <v>100</v>
       </c>
       <c r="AB10" s="44" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
     </row>
     <row r="11" spans="1:28" x14ac:dyDescent="0.3">
@@ -67931,10 +67970,10 @@
         <v>9</v>
       </c>
       <c r="B11" s="23" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="C11" s="49" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="D11" s="49" t="s">
         <v>180</v>
@@ -67946,7 +67985,7 @@
         <v>261571</v>
       </c>
       <c r="G11" s="49" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="H11" s="49">
         <v>2000</v>
@@ -67991,7 +68030,7 @@
         <v>2.6100000000000002E-2</v>
       </c>
       <c r="V11" s="44" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="W11" s="44" t="s">
         <v>36</v>
@@ -68009,7 +68048,7 @@
         <v>44</v>
       </c>
       <c r="AB11" s="44" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
     </row>
     <row r="12" spans="1:28" x14ac:dyDescent="0.3">
@@ -68147,7 +68186,7 @@
   <sheetData>
     <row r="1" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="56" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="B1" s="56" t="s">
         <v>32</v>
@@ -68337,7 +68376,7 @@
         <v>261574</v>
       </c>
       <c r="G3" s="38" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="H3" s="38">
         <v>330</v>
@@ -68400,7 +68439,7 @@
         <v>44</v>
       </c>
       <c r="AB3" s="38" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
     </row>
     <row r="4" spans="1:28" x14ac:dyDescent="0.3">
@@ -68423,7 +68462,7 @@
         <v>261573</v>
       </c>
       <c r="G4" s="38" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="H4" s="38">
         <v>600</v>
@@ -68435,7 +68474,7 @@
         <v>2.08</v>
       </c>
       <c r="K4" s="38" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="L4" s="40">
         <v>801.21600000000001</v>
@@ -68486,7 +68525,7 @@
         <v>40</v>
       </c>
       <c r="AB4" s="38" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
     </row>
     <row r="5" spans="1:28" x14ac:dyDescent="0.3">
@@ -68509,7 +68548,7 @@
         <v>261575</v>
       </c>
       <c r="G5" s="38" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="H5" s="38">
         <v>1100</v>
@@ -68521,7 +68560,7 @@
         <v>2.08</v>
       </c>
       <c r="K5" s="38" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="L5" s="40">
         <v>1468.896</v>
@@ -68572,7 +68611,7 @@
         <v>93</v>
       </c>
       <c r="AB5" s="38" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
     </row>
     <row r="6" spans="1:28" x14ac:dyDescent="0.3">
@@ -68595,7 +68634,7 @@
         <v>261582</v>
       </c>
       <c r="G6" s="38" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="H6" s="38">
         <v>800</v>
@@ -68607,7 +68646,7 @@
         <v>1.51</v>
       </c>
       <c r="K6" s="38" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="L6" s="40">
         <v>686.14400000000001</v>
@@ -68658,7 +68697,7 @@
         <v>37</v>
       </c>
       <c r="AB6" s="38" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
     </row>
     <row r="7" spans="1:28" x14ac:dyDescent="0.3">
@@ -68681,7 +68720,7 @@
         <v>261577</v>
       </c>
       <c r="G7" s="38" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="H7" s="38">
         <v>4000</v>
@@ -68741,10 +68780,10 @@
         <v>35</v>
       </c>
       <c r="AA7" s="38" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="AB7" s="38" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
     </row>
     <row r="8" spans="1:28" x14ac:dyDescent="0.3">
@@ -68767,7 +68806,7 @@
         <v>261581</v>
       </c>
       <c r="G8" s="38" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="H8" s="38">
         <v>1000</v>
@@ -68779,7 +68818,7 @@
         <v>1.21</v>
       </c>
       <c r="K8" s="38" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="L8" s="40">
         <v>561.44000000000005</v>
@@ -68830,7 +68869,7 @@
         <v>37</v>
       </c>
       <c r="AB8" s="38" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
     </row>
     <row r="9" spans="1:28" x14ac:dyDescent="0.3">
@@ -68853,7 +68892,7 @@
         <v>261576</v>
       </c>
       <c r="G9" s="38" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="H9" s="38">
         <v>700</v>
@@ -68865,7 +68904,7 @@
         <v>1.43</v>
       </c>
       <c r="K9" s="38" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="L9" s="40">
         <v>900.9</v>
@@ -68916,7 +68955,7 @@
         <v>40</v>
       </c>
       <c r="AB9" s="38" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
     </row>
     <row r="10" spans="1:28" x14ac:dyDescent="0.3">
@@ -68939,7 +68978,7 @@
         <v>261580</v>
       </c>
       <c r="G10" s="38" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="H10" s="38">
         <v>1100</v>
@@ -68951,7 +68990,7 @@
         <v>1.47</v>
       </c>
       <c r="K10" s="38" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="L10" s="40">
         <v>1149.6869999999999</v>
@@ -69002,7 +69041,7 @@
         <v>37</v>
       </c>
       <c r="AB10" s="38" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
     </row>
     <row r="11" spans="1:28" x14ac:dyDescent="0.3">
@@ -69025,7 +69064,7 @@
         <v>261578</v>
       </c>
       <c r="G11" s="38" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="H11" s="38">
         <v>1100</v>
@@ -69037,7 +69076,7 @@
         <v>1.59</v>
       </c>
       <c r="K11" s="38" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="L11" s="40">
         <v>912.97799999999995</v>
@@ -69088,7 +69127,7 @@
         <v>44</v>
       </c>
       <c r="AB11" s="38" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
     </row>
     <row r="12" spans="1:28" x14ac:dyDescent="0.3">
@@ -69111,7 +69150,7 @@
         <v>261579</v>
       </c>
       <c r="G12" s="38" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="H12" s="38">
         <v>700</v>
@@ -69123,7 +69162,7 @@
         <v>1.8</v>
       </c>
       <c r="K12" s="38" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="L12" s="40">
         <v>1002.96</v>
@@ -69174,7 +69213,7 @@
         <v>44</v>
       </c>
       <c r="AB12" s="38" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
     </row>
     <row r="13" spans="1:28" x14ac:dyDescent="0.3">
@@ -69304,7 +69343,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F13C72A1-3D66-4763-9C45-BFA286988A3B}">
-  <dimension ref="A1:AB16"/>
+  <dimension ref="A1:AB17"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="3.5546875" style="20" customWidth="1"/>
@@ -69316,7 +69355,7 @@
     <col min="7" max="7" width="10.44140625" style="20" customWidth="1"/>
     <col min="8" max="8" width="6.88671875" style="20" customWidth="1"/>
     <col min="9" max="9" width="7" style="20" customWidth="1"/>
-    <col min="10" max="10" width="7.21875" style="20" customWidth="1"/>
+    <col min="10" max="10" width="9.88671875" style="20" customWidth="1"/>
     <col min="11" max="11" width="14.109375" style="20" customWidth="1"/>
     <col min="12" max="12" width="9.77734375" style="20" hidden="1" customWidth="1"/>
     <col min="13" max="13" width="8.77734375" style="20" hidden="1" customWidth="1"/>
@@ -69338,7 +69377,7 @@
   <sheetData>
     <row r="1" spans="1:28" ht="18" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="56" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="B1" s="56" t="s">
         <v>32</v>
@@ -69516,7 +69555,7 @@
         <v>75</v>
       </c>
       <c r="C3" s="38" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="D3" s="38" t="s">
         <v>180</v>
@@ -69528,7 +69567,7 @@
         <v>261589</v>
       </c>
       <c r="G3" s="38" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="H3" s="38">
         <v>450</v>
@@ -69540,7 +69579,7 @@
         <v>2.5099999999999998</v>
       </c>
       <c r="K3" s="38" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="L3" s="40">
         <v>1339.587</v>
@@ -69582,7 +69621,7 @@
         <v>35</v>
       </c>
       <c r="Y3" s="38" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="Z3" s="38" t="s">
         <v>36</v>
@@ -69591,7 +69630,7 @@
         <v>37</v>
       </c>
       <c r="AB3" s="38" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
     </row>
     <row r="4" spans="1:28" x14ac:dyDescent="0.3">
@@ -69602,7 +69641,7 @@
         <v>75</v>
       </c>
       <c r="C4" s="38" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="D4" s="38" t="s">
         <v>180</v>
@@ -69614,7 +69653,7 @@
         <v>261587</v>
       </c>
       <c r="G4" s="38" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="H4" s="38">
         <v>200</v>
@@ -69626,7 +69665,7 @@
         <v>2.29</v>
       </c>
       <c r="K4" s="38" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="L4" s="40">
         <v>481.358</v>
@@ -69668,7 +69707,7 @@
         <v>35</v>
       </c>
       <c r="Y4" s="38" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="Z4" s="38" t="s">
         <v>36</v>
@@ -69677,7 +69716,7 @@
         <v>44</v>
       </c>
       <c r="AB4" s="38" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
     </row>
     <row r="5" spans="1:28" x14ac:dyDescent="0.3">
@@ -69700,7 +69739,7 @@
         <v>261588</v>
       </c>
       <c r="G5" s="38" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="H5" s="38">
         <v>510</v>
@@ -69754,7 +69793,7 @@
         <v>60</v>
       </c>
       <c r="Y5" s="38" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="Z5" s="38" t="s">
         <v>60</v>
@@ -69763,7 +69802,7 @@
         <v>44</v>
       </c>
       <c r="AB5" s="38" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
     </row>
     <row r="6" spans="1:28" x14ac:dyDescent="0.3">
@@ -69774,7 +69813,7 @@
         <v>75</v>
       </c>
       <c r="C6" s="38" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="D6" s="38" t="s">
         <v>180</v>
@@ -69786,7 +69825,7 @@
         <v>261593</v>
       </c>
       <c r="G6" s="38" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="H6" s="38">
         <v>775</v>
@@ -69798,7 +69837,7 @@
         <v>1.35</v>
       </c>
       <c r="K6" s="38" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="L6" s="40">
         <v>502.2</v>
@@ -69840,7 +69879,7 @@
         <v>35</v>
       </c>
       <c r="Y6" s="38" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="Z6" s="38" t="s">
         <v>36</v>
@@ -69849,7 +69888,7 @@
         <v>44</v>
       </c>
       <c r="AB6" s="38" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
     </row>
     <row r="7" spans="1:28" x14ac:dyDescent="0.3">
@@ -69860,7 +69899,7 @@
         <v>75</v>
       </c>
       <c r="C7" s="38" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="D7" s="38" t="s">
         <v>180</v>
@@ -69872,7 +69911,7 @@
         <v>261590</v>
       </c>
       <c r="G7" s="38" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="H7" s="38">
         <v>500</v>
@@ -69884,7 +69923,7 @@
         <v>1.2</v>
       </c>
       <c r="K7" s="38" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="L7" s="40">
         <v>259.2</v>
@@ -69926,7 +69965,7 @@
         <v>35</v>
       </c>
       <c r="Y7" s="38" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="Z7" s="38" t="s">
         <v>36</v>
@@ -69935,7 +69974,7 @@
         <v>44</v>
       </c>
       <c r="AB7" s="38" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
     </row>
     <row r="8" spans="1:28" x14ac:dyDescent="0.3">
@@ -69958,7 +69997,7 @@
         <v>261586</v>
       </c>
       <c r="G8" s="38" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="H8" s="38">
         <v>980</v>
@@ -69970,7 +70009,7 @@
         <v>1.9219999999999999</v>
       </c>
       <c r="K8" s="38" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="L8" s="40">
         <v>1203.595</v>
@@ -70021,7 +70060,7 @@
         <v>40</v>
       </c>
       <c r="AB8" s="38" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
     </row>
     <row r="9" spans="1:28" x14ac:dyDescent="0.3">
@@ -70044,7 +70083,7 @@
         <v>261583</v>
       </c>
       <c r="G9" s="38" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="H9" s="38">
         <v>500</v>
@@ -70056,7 +70095,7 @@
         <v>1.6619999999999999</v>
       </c>
       <c r="K9" s="38" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="L9" s="40">
         <v>471.17700000000002</v>
@@ -70107,7 +70146,7 @@
         <v>100</v>
       </c>
       <c r="AB9" s="38" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
     </row>
     <row r="10" spans="1:28" x14ac:dyDescent="0.3">
@@ -70130,7 +70169,7 @@
         <v>261595</v>
       </c>
       <c r="G10" s="38" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="H10" s="38">
         <v>700</v>
@@ -70142,7 +70181,7 @@
         <v>1.99</v>
       </c>
       <c r="K10" s="38" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="L10" s="40">
         <v>794.01</v>
@@ -70193,7 +70232,7 @@
         <v>44</v>
       </c>
       <c r="AB10" s="38" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
     </row>
     <row r="11" spans="1:28" x14ac:dyDescent="0.3">
@@ -70216,7 +70255,7 @@
         <v>261594</v>
       </c>
       <c r="G11" s="38" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="H11" s="38">
         <v>1500</v>
@@ -70228,7 +70267,7 @@
         <v>1.59</v>
       </c>
       <c r="K11" s="38" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="L11" s="40">
         <v>1216.3499999999999</v>
@@ -70279,7 +70318,7 @@
         <v>37</v>
       </c>
       <c r="AB11" s="38" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
     </row>
     <row r="12" spans="1:28" x14ac:dyDescent="0.3">
@@ -70290,82 +70329,76 @@
         <v>75</v>
       </c>
       <c r="C12" s="38" t="s">
-        <v>102</v>
-      </c>
-      <c r="D12" s="38" t="s">
-        <v>180</v>
-      </c>
-      <c r="E12" s="38" t="s">
-        <v>32</v>
-      </c>
+        <v>80</v>
+      </c>
+      <c r="D12" s="57">
+        <v>46206</v>
+      </c>
+      <c r="E12" s="38"/>
       <c r="F12" s="38">
-        <v>261585</v>
-      </c>
-      <c r="G12" s="38" t="s">
-        <v>223</v>
+        <v>261596</v>
+      </c>
+      <c r="G12" s="59" t="s">
+        <v>261</v>
       </c>
       <c r="H12" s="38">
-        <v>675</v>
-      </c>
-      <c r="I12" s="40">
-        <v>0.51200000000000001</v>
+        <v>600</v>
+      </c>
+      <c r="I12" s="40" t="s">
+        <v>250</v>
       </c>
       <c r="J12" s="40">
-        <v>1.5620000000000001</v>
+        <v>1.93</v>
       </c>
       <c r="K12" s="38" t="s">
-        <v>227</v>
+        <v>251</v>
       </c>
       <c r="L12" s="40">
-        <v>539.827</v>
-      </c>
-      <c r="M12" s="42">
-        <v>527.20000000000005</v>
-      </c>
-      <c r="N12" s="39">
-        <v>7.3200000000000001E-2</v>
-      </c>
-      <c r="O12" s="41">
-        <v>4.3899999999999997</v>
-      </c>
-      <c r="P12" s="38">
-        <v>209.5</v>
+        <v>1007460</v>
+      </c>
+      <c r="M12" s="42" t="s">
+        <v>252</v>
+      </c>
+      <c r="N12" s="39" t="s">
+        <v>253</v>
+      </c>
+      <c r="O12" s="41" t="s">
+        <v>254</v>
+      </c>
+      <c r="P12" s="38" t="s">
+        <v>255</v>
       </c>
       <c r="Q12" s="38">
+        <v>1</v>
+      </c>
+      <c r="R12" s="38">
+        <v>900</v>
+      </c>
+      <c r="S12" s="40" t="s">
+        <v>250</v>
+      </c>
+      <c r="T12" s="38">
+        <v>30</v>
+      </c>
+      <c r="U12" s="39" t="s">
+        <v>256</v>
+      </c>
+      <c r="V12" s="38" t="s">
+        <v>83</v>
+      </c>
+      <c r="W12" s="38" t="s">
+        <v>83</v>
+      </c>
+      <c r="X12" s="38" t="s">
+        <v>83</v>
+      </c>
+      <c r="Y12" s="38"/>
+      <c r="Z12" s="38"/>
+      <c r="AA12" s="38">
         <v>2</v>
       </c>
-      <c r="R12" s="38">
-        <v>1050</v>
-      </c>
-      <c r="S12" s="40">
-        <v>1.024</v>
-      </c>
-      <c r="T12" s="38">
-        <v>26</v>
-      </c>
-      <c r="U12" s="39">
-        <v>2.4799999999999999E-2</v>
-      </c>
-      <c r="V12" s="38" t="s">
-        <v>104</v>
-      </c>
-      <c r="W12" s="38" t="s">
-        <v>36</v>
-      </c>
-      <c r="X12" s="38" t="s">
-        <v>36</v>
-      </c>
-      <c r="Y12" s="38" t="s">
-        <v>32</v>
-      </c>
-      <c r="Z12" s="38" t="s">
-        <v>32</v>
-      </c>
-      <c r="AA12" s="38" t="s">
-        <v>100</v>
-      </c>
       <c r="AB12" s="38" t="s">
-        <v>226</v>
+        <v>257</v>
       </c>
     </row>
     <row r="13" spans="1:28" x14ac:dyDescent="0.3">
@@ -70376,7 +70409,7 @@
         <v>75</v>
       </c>
       <c r="C13" s="38" t="s">
-        <v>74</v>
+        <v>102</v>
       </c>
       <c r="D13" s="38" t="s">
         <v>180</v>
@@ -70385,58 +70418,58 @@
         <v>32</v>
       </c>
       <c r="F13" s="38">
-        <v>261591</v>
+        <v>261585</v>
       </c>
       <c r="G13" s="38" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="H13" s="38">
-        <v>600</v>
+        <v>675</v>
       </c>
       <c r="I13" s="40">
-        <v>0.47</v>
+        <v>0.51200000000000001</v>
       </c>
       <c r="J13" s="40">
-        <v>1.53</v>
+        <v>1.5620000000000001</v>
       </c>
       <c r="K13" s="38" t="s">
         <v>225</v>
       </c>
       <c r="L13" s="40">
-        <v>431.46</v>
+        <v>539.827</v>
       </c>
       <c r="M13" s="42">
-        <v>459</v>
+        <v>527.20000000000005</v>
       </c>
       <c r="N13" s="39">
-        <v>6.3799999999999996E-2</v>
+        <v>7.3200000000000001E-2</v>
       </c>
       <c r="O13" s="41">
-        <v>3.83</v>
+        <v>4.3899999999999997</v>
       </c>
       <c r="P13" s="38">
-        <v>157.5</v>
+        <v>209.5</v>
       </c>
       <c r="Q13" s="38">
         <v>2</v>
       </c>
       <c r="R13" s="38">
-        <v>1000</v>
+        <v>1050</v>
       </c>
       <c r="S13" s="40">
-        <v>0.94</v>
+        <v>1.024</v>
       </c>
       <c r="T13" s="38">
-        <v>60</v>
+        <v>26</v>
       </c>
       <c r="U13" s="39">
-        <v>0.06</v>
+        <v>2.4799999999999999E-2</v>
       </c>
       <c r="V13" s="38" t="s">
+        <v>104</v>
+      </c>
+      <c r="W13" s="38" t="s">
         <v>36</v>
-      </c>
-      <c r="W13" s="38" t="s">
-        <v>35</v>
       </c>
       <c r="X13" s="38" t="s">
         <v>36</v>
@@ -70462,7 +70495,7 @@
         <v>75</v>
       </c>
       <c r="C14" s="38" t="s">
-        <v>102</v>
+        <v>74</v>
       </c>
       <c r="D14" s="38" t="s">
         <v>180</v>
@@ -70471,58 +70504,58 @@
         <v>32</v>
       </c>
       <c r="F14" s="38">
-        <v>261584</v>
+        <v>261591</v>
       </c>
       <c r="G14" s="38" t="s">
+        <v>218</v>
+      </c>
+      <c r="H14" s="38">
+        <v>600</v>
+      </c>
+      <c r="I14" s="40">
+        <v>0.47</v>
+      </c>
+      <c r="J14" s="40">
+        <v>1.53</v>
+      </c>
+      <c r="K14" s="38" t="s">
         <v>223</v>
       </c>
-      <c r="H14" s="38">
-        <v>820</v>
-      </c>
-      <c r="I14" s="40">
-        <v>0.41899999999999998</v>
-      </c>
-      <c r="J14" s="40">
-        <v>1.3879999999999999</v>
-      </c>
-      <c r="K14" s="38" t="s">
-        <v>222</v>
-      </c>
       <c r="L14" s="40">
-        <v>476.88900000000001</v>
+        <v>431.46</v>
       </c>
       <c r="M14" s="42">
-        <v>569.1</v>
+        <v>459</v>
       </c>
       <c r="N14" s="39">
-        <v>7.9000000000000001E-2</v>
+        <v>6.3799999999999996E-2</v>
       </c>
       <c r="O14" s="41">
-        <v>4.74</v>
+        <v>3.83</v>
       </c>
       <c r="P14" s="38">
-        <v>185</v>
+        <v>157.5</v>
       </c>
       <c r="Q14" s="38">
         <v>2</v>
       </c>
       <c r="R14" s="38">
-        <v>900</v>
+        <v>1000</v>
       </c>
       <c r="S14" s="40">
-        <v>0.83799999999999997</v>
+        <v>0.94</v>
       </c>
       <c r="T14" s="38">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="U14" s="39">
-        <v>6.8900000000000003E-2</v>
+        <v>0.06</v>
       </c>
       <c r="V14" s="38" t="s">
-        <v>104</v>
+        <v>36</v>
       </c>
       <c r="W14" s="38" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="X14" s="38" t="s">
         <v>36</v>
@@ -70534,10 +70567,10 @@
         <v>32</v>
       </c>
       <c r="AA14" s="38" t="s">
-        <v>44</v>
+        <v>100</v>
       </c>
       <c r="AB14" s="38" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
     </row>
     <row r="15" spans="1:28" x14ac:dyDescent="0.3">
@@ -70548,7 +70581,7 @@
         <v>75</v>
       </c>
       <c r="C15" s="38" t="s">
-        <v>66</v>
+        <v>102</v>
       </c>
       <c r="D15" s="38" t="s">
         <v>180</v>
@@ -70557,37 +70590,37 @@
         <v>32</v>
       </c>
       <c r="F15" s="38">
-        <v>261592</v>
+        <v>261584</v>
       </c>
       <c r="G15" s="38" t="s">
+        <v>221</v>
+      </c>
+      <c r="H15" s="38">
+        <v>820</v>
+      </c>
+      <c r="I15" s="40">
+        <v>0.41899999999999998</v>
+      </c>
+      <c r="J15" s="40">
+        <v>1.3879999999999999</v>
+      </c>
+      <c r="K15" s="38" t="s">
         <v>220</v>
       </c>
-      <c r="H15" s="38">
-        <v>765</v>
-      </c>
-      <c r="I15" s="40">
-        <v>0.44</v>
-      </c>
-      <c r="J15" s="40">
-        <v>1.49</v>
-      </c>
-      <c r="K15" s="38" t="s">
-        <v>219</v>
-      </c>
       <c r="L15" s="40">
-        <v>501.53399999999999</v>
+        <v>476.88900000000001</v>
       </c>
       <c r="M15" s="42">
-        <v>569.9</v>
+        <v>569.1</v>
       </c>
       <c r="N15" s="39">
-        <v>7.9200000000000007E-2</v>
+        <v>7.9000000000000001E-2</v>
       </c>
       <c r="O15" s="41">
-        <v>4.75</v>
+        <v>4.74</v>
       </c>
       <c r="P15" s="38">
-        <v>173</v>
+        <v>185</v>
       </c>
       <c r="Q15" s="38">
         <v>2</v>
@@ -70596,22 +70629,22 @@
         <v>900</v>
       </c>
       <c r="S15" s="40">
-        <v>0.88</v>
+        <v>0.83799999999999997</v>
       </c>
       <c r="T15" s="38">
-        <v>20</v>
+        <v>62</v>
       </c>
       <c r="U15" s="39">
-        <v>2.2200000000000001E-2</v>
+        <v>6.8900000000000003E-2</v>
       </c>
       <c r="V15" s="38" t="s">
-        <v>35</v>
+        <v>104</v>
       </c>
       <c r="W15" s="38" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="X15" s="38" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="Y15" s="38" t="s">
         <v>32</v>
@@ -70620,95 +70653,181 @@
         <v>32</v>
       </c>
       <c r="AA15" s="38" t="s">
+        <v>44</v>
+      </c>
+      <c r="AB15" s="38" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="16" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A16" s="38">
+        <v>14</v>
+      </c>
+      <c r="B16" s="43" t="s">
+        <v>75</v>
+      </c>
+      <c r="C16" s="38" t="s">
+        <v>66</v>
+      </c>
+      <c r="D16" s="38" t="s">
+        <v>180</v>
+      </c>
+      <c r="E16" s="38" t="s">
+        <v>32</v>
+      </c>
+      <c r="F16" s="38">
+        <v>261592</v>
+      </c>
+      <c r="G16" s="38" t="s">
+        <v>218</v>
+      </c>
+      <c r="H16" s="38">
+        <v>765</v>
+      </c>
+      <c r="I16" s="40">
+        <v>0.44</v>
+      </c>
+      <c r="J16" s="40">
+        <v>1.49</v>
+      </c>
+      <c r="K16" s="38" t="s">
+        <v>217</v>
+      </c>
+      <c r="L16" s="40">
+        <v>501.53399999999999</v>
+      </c>
+      <c r="M16" s="42">
+        <v>569.9</v>
+      </c>
+      <c r="N16" s="39">
+        <v>7.9200000000000007E-2</v>
+      </c>
+      <c r="O16" s="41">
+        <v>4.75</v>
+      </c>
+      <c r="P16" s="38">
+        <v>173</v>
+      </c>
+      <c r="Q16" s="38">
+        <v>2</v>
+      </c>
+      <c r="R16" s="38">
+        <v>900</v>
+      </c>
+      <c r="S16" s="40">
+        <v>0.88</v>
+      </c>
+      <c r="T16" s="38">
+        <v>20</v>
+      </c>
+      <c r="U16" s="39">
+        <v>2.2200000000000001E-2</v>
+      </c>
+      <c r="V16" s="38" t="s">
+        <v>35</v>
+      </c>
+      <c r="W16" s="38" t="s">
+        <v>35</v>
+      </c>
+      <c r="X16" s="38" t="s">
+        <v>35</v>
+      </c>
+      <c r="Y16" s="38" t="s">
+        <v>32</v>
+      </c>
+      <c r="Z16" s="38" t="s">
+        <v>32</v>
+      </c>
+      <c r="AA16" s="38" t="s">
         <v>100</v>
       </c>
-      <c r="AB15" s="38" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="16" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A16" s="37" t="s">
+      <c r="AB16" s="38" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="17" spans="1:28" x14ac:dyDescent="0.3">
+      <c r="A17" s="37" t="s">
         <v>32</v>
       </c>
-      <c r="B16" s="37" t="s">
+      <c r="B17" s="37" t="s">
         <v>32</v>
       </c>
-      <c r="C16" s="37" t="s">
+      <c r="C17" s="37" t="s">
         <v>32</v>
       </c>
-      <c r="D16" s="37" t="s">
+      <c r="D17" s="37" t="s">
         <v>32</v>
       </c>
-      <c r="E16" s="37" t="s">
+      <c r="E17" s="37" t="s">
         <v>32</v>
       </c>
-      <c r="F16" s="37" t="s">
+      <c r="F17" s="37" t="s">
         <v>32</v>
       </c>
-      <c r="G16" s="37" t="s">
+      <c r="G17" s="37" t="s">
         <v>32</v>
       </c>
-      <c r="H16" s="37">
+      <c r="H17" s="37">
         <v>8975</v>
       </c>
-      <c r="I16" s="37" t="s">
+      <c r="I17" s="37" t="s">
         <v>32</v>
       </c>
-      <c r="J16" s="37" t="s">
+      <c r="J17" s="37" t="s">
         <v>32</v>
       </c>
-      <c r="K16" s="37" t="s">
+      <c r="K17" s="37" t="s">
         <v>32</v>
       </c>
-      <c r="L16" s="37" t="s">
+      <c r="L17" s="37" t="s">
         <v>32</v>
       </c>
-      <c r="M16" s="37" t="s">
+      <c r="M17" s="37" t="s">
         <v>32</v>
       </c>
-      <c r="N16" s="37" t="s">
+      <c r="N17" s="37" t="s">
         <v>32</v>
       </c>
-      <c r="O16" s="37" t="s">
+      <c r="O17" s="37" t="s">
         <v>32</v>
       </c>
-      <c r="P16" s="37">
+      <c r="P17" s="37">
         <v>4181.8</v>
       </c>
-      <c r="Q16" s="37" t="s">
+      <c r="Q17" s="37" t="s">
         <v>32</v>
       </c>
-      <c r="R16" s="37" t="s">
+      <c r="R17" s="37" t="s">
         <v>32</v>
       </c>
-      <c r="S16" s="37" t="s">
+      <c r="S17" s="37" t="s">
         <v>32</v>
       </c>
-      <c r="T16" s="37" t="s">
+      <c r="T17" s="37" t="s">
         <v>32</v>
       </c>
-      <c r="U16" s="37" t="s">
+      <c r="U17" s="37" t="s">
         <v>32</v>
       </c>
-      <c r="V16" s="37" t="s">
+      <c r="V17" s="37" t="s">
         <v>32</v>
       </c>
-      <c r="W16" s="37" t="s">
+      <c r="W17" s="37" t="s">
         <v>32</v>
       </c>
-      <c r="X16" s="37" t="s">
+      <c r="X17" s="37" t="s">
         <v>32</v>
       </c>
-      <c r="Y16" s="37" t="s">
+      <c r="Y17" s="37" t="s">
         <v>32</v>
       </c>
-      <c r="Z16" s="37" t="s">
+      <c r="Z17" s="37" t="s">
         <v>32</v>
       </c>
-      <c r="AA16" s="37" t="s">
+      <c r="AA17" s="37" t="s">
         <v>32</v>
       </c>
-      <c r="AB16" s="37" t="s">
+      <c r="AB17" s="37" t="s">
         <v>32</v>
       </c>
     </row>

--- a/programacao-hoje.xlsx
+++ b/programacao-hoje.xlsx
@@ -8,23 +8,23 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Meu Drive\Prime\Produção\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DCE5BE7A-0879-425D-8FAB-EDF0219C8141}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E1EC9845-4FC4-481D-925F-9D76C86E5E51}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="1" activeTab="7" xr2:uid="{B44A584A-541A-489B-A537-1CEFC190DF9A}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="1" activeTab="4" xr2:uid="{B44A584A-541A-489B-A537-1CEFC190DF9A}"/>
   </bookViews>
   <sheets>
     <sheet name="FAVINCO 18 ao 25" sheetId="5" r:id="rId1"/>
     <sheet name="ABAPEL" sheetId="2" r:id="rId2"/>
     <sheet name="HARMONY5" sheetId="6" r:id="rId3"/>
     <sheet name="RM Embalagens" sheetId="7" r:id="rId4"/>
-    <sheet name="CURITIBOX" sheetId="8" r:id="rId5"/>
+    <sheet name="A4 e JFER" sheetId="8" r:id="rId5"/>
     <sheet name="DR Embalagem" sheetId="9" r:id="rId6"/>
     <sheet name="ABAPEL3" sheetId="10" r:id="rId7"/>
     <sheet name="FAVINCO" sheetId="11" r:id="rId8"/>
   </sheets>
   <definedNames>
+    <definedName name="_xlnm.Print_Area" localSheetId="4">'A4 e JFER'!$A$1:$AB$5</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="6">ABAPEL3!$A$1:$AB$13</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="4">CURITIBOX!$A$1:$AB$5</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="5">'DR Embalagem'!$A$1:$AB$12</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="3">'RM Embalagens'!$A$1:$AB$17</definedName>
   </definedNames>
